--- a/eval/learning-curve/results/learning_curve_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2012-2020 or 2010-2020</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2010 to 2020</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1938,17 +1938,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>didanosine, abacavir, zidovudine, stavudine, delavirdine, nevirapine, efavirenz, nelfinavir, elvitegravir, raltegravir</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1983,12 +1983,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>37272233</t>
+          <t>37279764</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>didanosine, abacavir, zidovudine, stavudine, delavirdine, nevirapine, efavirenz, nelfinavir, elvitegravir, raltegravir</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2008,22 +2008,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>37279764</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2058,22 +2058,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>37358226</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Abacavir, Zidovudine, TDF, Efavirenz, Nevirapine, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2108,12 +2108,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>37358226</t>
+          <t>37381002</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Abacavir, Zidovudine, TDF, Efavirenz, Nevirapine, Lamivudine, Dolutegravir</t>
+          <t>NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2133,22 +2133,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>37381002</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NFLG, PR, RT, IN, Pol</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Protease (PR), Reverse Transcriptase (RT), Near Full Length Genomes (NFLG)</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2158,12 +2158,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>37381002</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>EFV, NVP, RPV, ETR, DOR</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2183,22 +2183,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>37381002</t>
+          <t>37495103</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Not explicitly listed</t>
+          <t>ABI PRISM sequencing</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2208,22 +2208,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>37439411</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>RNA</t>
+          <t>K03455</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2233,22 +2233,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>37439411</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NFLG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>EFV, NVP, RPV, ETR, DOR</t>
+          <t>Gag, Pol, Env, Integnase RT</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2258,7 +2258,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>37495103</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ABI PRISM sequencing</t>
+          <t>Next-Generation Sequencing (NGS)</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2288,17 +2288,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>K03455</t>
+          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2308,22 +2308,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>37515146</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NFLG</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Gag, Pol, Env, Integnase RT</t>
+          <t>ABI 3500</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2333,22 +2333,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>37515146</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Next-Generation Sequencing (NGS)</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2358,22 +2358,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>2016-2017, 2019-2020</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2383,22 +2383,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>37515095</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Pol</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PR, RT</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2408,22 +2408,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>37515146</t>
+          <t>37520425</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Pol</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Protease and reverse transcriptase</t>
+          <t>EFV, ATV, FTC, TDF</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2433,22 +2433,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>37515146</t>
+          <t>37540331</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ABI 3500</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2458,12 +2458,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>37515146</t>
+          <t>37540331</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Tenofovir, Dolutegravir, Efavirenz, Lopinavir, Atazanavir</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2483,22 +2483,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2016-2017, 2019-2020</t>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2508,22 +2508,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2533,22 +2533,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>PI, INSTI</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EFV, ATV, FTC, TDF</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2558,22 +2558,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>37540331</t>
+          <t>37541705</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2583,7 +2583,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>37540331</t>
+          <t>37546367</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tenofovir, Dolutegravir, Efavirenz, Lopinavir, Atazanavir</t>
+          <t>AZT, ABC, FTC, 3TC, TDF, D4T, DDI, EFV, NVP, RPV, ETR, DOR, NFV, DRV</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2608,22 +2608,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2633,22 +2633,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2658,22 +2658,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37554471</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2683,22 +2683,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>37593123</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2708,22 +2708,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>37546367</t>
+          <t>37626789</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2007-2019</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AZT, ABC, FTC, 3TC, TDF, D4T, DDI, EFV, NVP, RPV, ETR, DOR, NFV, DRV</t>
+          <t>2017 to 2019</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2733,22 +2733,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>37626789</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ABI-3730 DNA genetic analyzer</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2758,7 +2758,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>37632071</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>NRTI, INSTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2783,22 +2783,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>37674678</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
+          <t>ABI 3730XL</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2808,22 +2808,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>37593123</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2833,7 +2833,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>37626789</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2007-2019</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2017 to 2019</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -2858,22 +2858,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>37626789</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ABI-3730 DNA genetic analyzer</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -2883,22 +2883,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>37632026</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Pol</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Protease and reverse-transcriptase regions</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -2908,7 +2908,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>37632071</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NRTI, INSTI, NNRTI, PI</t>
+          <t>NRTIs, INSTIs</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2933,22 +2933,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>37674678</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ABI 3730XL</t>
+          <t>Tenofovir, lamivudine, dolutegravir</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -2958,22 +2958,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37823653</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>NFLG, gp120</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>env</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2983,22 +2983,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37823653</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>plasma viral RNA</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3008,7 +3008,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37872202</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>gp120</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>None reported</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3033,22 +3033,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37878637</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3058,7 +3058,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NRTIs, INSTIs</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3083,7 +3083,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, dolutegravir</t>
+          <t>d4T, 3TC, AZT, NVP</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3108,22 +3108,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NFLG, gp120</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>env</t>
+          <t>MiSeq sequencing platform</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3133,22 +3133,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>plasma viral RNA</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3158,22 +3158,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>gp120</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>None reported</t>
+          <t>TDF, FTC, EFV</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3183,22 +3183,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37920909</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
+          <t>Viral RNA</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3208,22 +3208,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TDF, 3TC, EFV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>TDF, 3TC, EFV, PI</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3233,12 +3233,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37946329</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3258,7 +3258,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37946329</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>d4T, 3TC, AZT, NVP</t>
+          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3283,7 +3283,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>37896860</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Full genome, NFLG</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>RT, PI</t>
+          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3308,22 +3308,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>MiSeq sequencing platform</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3333,12 +3333,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3358,22 +3358,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37976185</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TDF, FTC, EFV</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3383,22 +3383,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>37920909</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Viral RNA</t>
+          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3408,7 +3408,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3433,7 +3433,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>38020274</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3458,7 +3458,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>38020274</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
+          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -3483,22 +3483,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Full genome, NFLG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -3508,12 +3508,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -3533,22 +3533,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -3558,22 +3558,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>HIV from plasma</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -3583,22 +3583,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>38072961</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3608,22 +3608,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -3633,22 +3633,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -3658,22 +3658,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -3683,22 +3683,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -3708,22 +3708,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -3733,22 +3733,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2020, 2022, 2023</t>
+          <t>BIC, FTC, TAF, EVG</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2020-2023</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3758,22 +3758,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>K03455</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -3783,12 +3783,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>HIV from plasma</t>
+          <t>NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -3808,22 +3808,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -3833,17 +3833,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3858,7 +3858,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>2008-2019</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2018-2019</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -3883,22 +3883,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>High-throughput sequencing</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -3908,22 +3908,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, PI, NNRTI</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -3933,22 +3933,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -3958,22 +3958,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF, EVG</t>
+          <t>RT, CA</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Gag, Pol</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -3983,12 +3983,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3998,285 +3998,10 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>K03455</t>
+          <t>Plasma viral RNA</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>38140553</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>PR, RT, IN, Pol</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>PR and part of RT</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>38140553</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Plasma; PBMC; Whole Blood</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Blood plasma, peripheral blood mononuclear cells, frozen whole blood</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>38140553</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>NRTIs, NNRTIs, PIs</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>38152686</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>38152686</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>38314093</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2008-2019</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2018-2019</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>38314093</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>NGS</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>High-throughput sequencing</t>
-        </is>
-      </c>
-      <c r="E150" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>38314093</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>NRTI, PI, NNRTI</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>38314093</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>38864613</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>RT, CA</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Gag, Pol</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>38864613</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Plasma viral RNA</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -513,17 +513,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sanger</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,22 +533,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21115794</t>
+          <t>19104010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HQ873097-HQ873169</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -558,12 +558,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27009474</t>
+          <t>21115794</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>HQ873097-HQ873169</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -583,12 +583,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27124362</t>
+          <t>21115794</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -608,22 +608,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27124362</t>
+          <t>23749954</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Virus isolates</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -633,22 +633,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28559249</t>
+          <t>24227862</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No evidence</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -658,22 +658,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29373677</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PBMC, Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>plasma RNA</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -683,12 +683,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30053052</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -708,12 +708,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30053052</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Didanosine (ddI), Emtricitabine (FTC), Lamivudine (3TC), Zidovudine (ZDV), Stavudine (d4T),Tenofovir disoproxil fumarate (TDF), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV)</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -733,22 +733,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>31988104</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>K03455, AF324493</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -758,22 +758,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>32601157</t>
+          <t>26311878</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -783,7 +783,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>33855437</t>
+          <t>26559830</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -808,12 +808,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>33855437</t>
+          <t>27009474</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>viral isolates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -833,7 +833,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>34516245</t>
+          <t>27009474</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Population sequencing</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -858,22 +858,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>35730213</t>
+          <t>27009474</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -883,22 +883,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>35730213</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EFV, DTG, TDF, 3TC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -908,22 +908,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -933,22 +933,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>27124362</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Virus isolates</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -958,22 +958,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>35913500</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -983,22 +983,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1008,22 +1006,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>28559249</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No evidence</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1033,22 +1031,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1058,7 +1056,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>29373677</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1068,12 +1066,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>plasma RNA</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1083,22 +1081,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>35945163</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>cobicistat-boosted darunavir, tenofovir alafenamide, emtricitabine, dolutegravir</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1108,22 +1106,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>36454248</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>51</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1133,22 +1129,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>36571282</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Clinical samples</t>
+          <t>gag-pol</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1158,22 +1154,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>36645792</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1183,22 +1179,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>36645792</t>
+          <t>30053052</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Abacavir (ABC), Didanosine (ddI), Emtricitabine (FTC), Lamivudine (3TC), Zidovudine (ZDV), Stavudine (d4T),Tenofovir disoproxil fumarate (TDF), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV)</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1208,22 +1204,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>31988104</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>K03455, AF324493</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1233,22 +1229,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>32601157</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1258,22 +1254,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1283,22 +1279,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1308,22 +1304,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36659824</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1333,22 +1329,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>33855437</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>viral isolates</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1358,22 +1354,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>34516245</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Population sequencing</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1383,22 +1379,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>36660819</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>NRTI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1408,7 +1404,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>36694270</t>
+          <t>35730213</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1418,12 +1414,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
+          <t>EFV, DTG, TDF, 3TC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, efavirenz, nevirapine, lopinavir, ritonavir</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1433,22 +1429,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>RT, IN</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>51</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>The paper does not specify which HIV genes were sequenced.</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1458,22 +1452,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>36706364</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>The paper does not specify the type of samples that were sequenced.</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1483,7 +1477,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>36738248</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1493,12 +1487,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2021-2022</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Data as of August 2021</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1508,22 +1502,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>36738248</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1533,22 +1527,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>36779485</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1558,22 +1552,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>36795586</t>
+          <t>35913500</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1583,22 +1577,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>36851704</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TDF, FTC, 3TC, ABC, ZDV, EVF, NVP, ATV/r, LPV/r, RAL, DTG, DRV/r, ETR, RPV, BIC, CAB</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1608,22 +1602,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>36851760</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Unspecified NRTIs, NNRTIs, PIs</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1633,22 +1625,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>36920025</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>UK, USA, Belgium, Canada, Netherlands, Switzerland, Portugal, Italy, South Korea, Spain</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Viral RNA from cultured virus</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1658,22 +1650,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plasma, CSF, PBMC</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1683,22 +1675,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>36931676</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1708,22 +1700,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>37017009</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Next-generation sequencing (Illumina MiSeq).</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1733,22 +1725,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>37039023</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NC_001802</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1758,22 +1750,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>37071019</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1783,22 +1775,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>37104815</t>
+          <t>35945163</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>cobicistat-boosted darunavir, tenofovir alafenamide, emtricitabine, dolutegravir</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1808,22 +1800,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>37104815</t>
+          <t>36415058</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Whole Blood, Semen</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Plasma RNA and HIV DNA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -1833,12 +1825,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>37112971</t>
+          <t>36454248</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1848,7 +1840,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>K03455 for PR-RT and INT regions</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1858,22 +1850,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>37147875</t>
+          <t>36571282</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Clinical samples</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1883,22 +1875,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>37147875</t>
+          <t>36597160</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir disoproxil fumarate (TDF)</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1908,22 +1898,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>37272233</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1933,22 +1923,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>37272233</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>120 * 76% = 95, or 120 or 129</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1958,22 +1948,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>37272233</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>didanosine, abacavir, zidovudine, stavudine, delavirdine, nevirapine, efavirenz, nelfinavir, elvitegravir, raltegravir</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1983,22 +1973,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>37279764</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2008,17 +1998,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36645792</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NNRTI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2033,22 +2023,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>37340869</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2058,22 +2048,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>37358226</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>14</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2083,22 +2071,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>37358226</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Abacavir, Zidovudine, TDF, Efavirenz, Nevirapine, Lamivudine, Dolutegravir</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -2108,22 +2096,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>37381002</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2133,22 +2121,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>37439411</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>RNA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2158,22 +2146,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>37439411</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EFV, NVP, RPV, ETR, DOR</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2183,22 +2171,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>37495103</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ABI PRISM sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2208,22 +2196,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>K03455</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2233,22 +2221,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>36659824</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NFLG</t>
+          <t>BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Gag, Pol, Env, Integnase RT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2258,22 +2246,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Next-Generation Sequencing (NGS)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2283,22 +2271,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>37498738</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2308,22 +2296,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>37515146</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ABI 3500</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2333,7 +2321,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>37515146</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2343,12 +2331,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -2358,22 +2346,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>36660819</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2016-2017, 2019-2020</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -2383,22 +2371,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>36694270</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Tenofovir, lamivudine, efavirenz, nevirapine, lopinavir, ritonavir</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2408,22 +2396,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>37520425</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DTG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EFV, ATV, FTC, TDF</t>
+          <t>No, the paper does not report HIV sequences from patient samples.</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2433,22 +2421,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>37540331</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>62 or 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs</t>
+          <t>The paper does not specify how many individuals had samples obtained for HIV sequencing.</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2458,22 +2446,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>37540331</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tenofovir, Dolutegravir, Efavirenz, Lopinavir, Atazanavir</t>
+          <t>The paper does not specify which HIV genes were sequenced.</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2483,22 +2471,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>36706364</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>The paper does not specify the type of samples that were sequenced.</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2508,22 +2496,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2020-2021</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>527</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>594</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2533,22 +2519,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Data as of August 2021</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2558,22 +2544,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>37541705</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2583,12 +2569,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>37546367</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2598,7 +2584,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AZT, ABC, FTC, 3TC, TDF, D4T, DDI, EFV, NVP, RPV, ETR, DOR, NFV, DRV</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2608,22 +2594,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>36738248</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2633,12 +2619,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2648,7 +2634,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2658,12 +2644,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>37554471</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2673,7 +2659,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2683,7 +2669,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>37593123</t>
+          <t>36779485</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2708,22 +2694,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>37626789</t>
+          <t>36795586</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2007-2019</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2017 to 2019</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2733,22 +2719,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>37626789</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ABI-3730 DNA genetic analyzer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2758,12 +2744,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>37632071</t>
+          <t>36851704</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2773,7 +2759,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NRTI, INSTI, NNRTI, PI</t>
+          <t>TDF, FTC, 3TC, ABC, ZDV, EVF, NVP, ATV/r, LPV/r, RAL, DTG, DRV/r, ETR, RPV, BIC, CAB</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2783,22 +2769,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>37674678</t>
+          <t>36851760</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ABI 3730XL</t>
+          <t>Unspecified NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2808,22 +2794,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2833,22 +2819,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>2020-2021</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -2858,22 +2842,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -2883,22 +2867,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -2908,12 +2892,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2923,7 +2907,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NRTIs, INSTIs</t>
+          <t>Viral RNA from cultured virus</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2933,12 +2917,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2948,7 +2932,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, dolutegravir</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -2958,22 +2942,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>36920025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NFLG, gp120</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>env</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -2983,7 +2967,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2993,12 +2977,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Plasma, CSF, PBMC</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>plasma viral RNA</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3008,22 +2992,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>gp120</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>None reported</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3033,22 +3017,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>36931676</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>DTG</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -3058,22 +3042,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>36961945</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3083,22 +3067,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>36967989</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>d4T, 3TC, AZT, NVP</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3108,7 +3092,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37017009</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3123,7 +3107,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>MiSeq sequencing platform</t>
+          <t>Next-generation sequencing (Illumina MiSeq).</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3133,22 +3117,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37029656</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3158,12 +3142,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37039023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3173,7 +3157,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>TDF, FTC, EFV</t>
+          <t>NC_001802</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -3183,22 +3167,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>37920909</t>
+          <t>37071019</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Viral RNA</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -3208,22 +3192,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37104815</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -3233,22 +3217,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37104815</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Whole Blood, Semen</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Plasma RNA and HIV DNA</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3258,12 +3242,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37112971</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3273,7 +3257,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
+          <t>K03455 for PR-RT and INT regions</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3283,22 +3267,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Full genome, NFLG</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3308,7 +3292,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3323,7 +3307,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3333,7 +3317,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>37147875</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3348,7 +3332,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
+          <t>Dolutegravir (DTG), Emtricitabine (FTC), Tenofovir disoproxil fumarate (TDF)</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3358,7 +3342,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3368,12 +3352,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -3383,22 +3367,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -3408,22 +3392,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3433,12 +3417,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3448,7 +3432,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -3458,7 +3442,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>37272233</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3473,7 +3457,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
+          <t>didanosine, abacavir, zidovudine, stavudine, delavirdine, nevirapine, efavirenz, nelfinavir, elvitegravir, raltegravir</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -3483,12 +3467,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>37279764</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3498,7 +3482,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -3508,22 +3492,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -3533,18 +3517,16 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>PR, RT, IN</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1651</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3558,22 +3540,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>HIV from plasma</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -3583,22 +3565,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3608,17 +3590,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>NNRTI, INSTI</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3633,17 +3615,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37340869</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3658,22 +3640,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37358226</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTIs, NNRTIs</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -3683,22 +3665,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37358226</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Abacavir, Zidovudine, TDF, Efavirenz, Nevirapine, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -3708,22 +3690,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37376649</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -3733,22 +3715,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>37376649</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF, EVG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3758,12 +3740,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>37381002</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3773,7 +3755,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>K03455</t>
+          <t>NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -3783,12 +3765,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3798,7 +3780,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -3808,22 +3790,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>38152686</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -3833,22 +3815,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>38152686</t>
+          <t>37439411</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>EFV, NVP, RPV, ETR, DOR</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3858,22 +3840,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>37495103</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2008-2019</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2018-2019</t>
+          <t>ABI PRISM sequencing</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -3883,22 +3865,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>High-throughput sequencing</t>
+          <t>K03455</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -3908,12 +3890,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3923,7 +3905,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -3933,22 +3915,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NFLG</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
+          <t>Gag, Pol, Env, Integnase RT</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -3958,22 +3940,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>38864613</t>
+          <t>37498738</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>RT, CA</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Gag, Pol</t>
+          <t>Next-Generation Sequencing (NGS)</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -3983,25 +3965,2940 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>37498738</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DTG</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>1. NRTIs: FTC, TDF, ABC, ZDV, 3TC, D4T 2. NNRTIs: RPV, NVP, EFV 3. PIs: LPV/RTV, DRV/RTV, IDV 4. INSTIs: RAL, ETV</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>37515095</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>37515146</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>379</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>37515146</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ABI 3500</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>37515146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2016-2017, 2019-2020</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>37520425</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>DTG</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>EFV, ATV, FTC, TDF</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>37537871</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>37537871</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>37537871</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>37540331</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>37540331</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>37540331</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Tenofovir, Dolutegravir, Efavirenz, Lopinavir, Atazanavir</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2020-2021</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>37541705</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Lopinavir/ritonavir, dolutegravir, raltegravir</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>37546367</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>AZT, ABC, FTC, 3TC, TDF, D4T, DDI, EFV, NVP, RPV, ETR, DOR, NFV, DRV</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>37554471</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz, Etravirine, Dolutegravir, Darunavir, Ritonavir</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>37573167</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Specific drugs not reported</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>37574435</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>37593123</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>37593123</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>37593123</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>37593123</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>37626789</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>551</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>37626789</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2007-2019</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2017 to 2019</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>37626789</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ABI-3730 DNA genetic analyzer</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>37632026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>PR, RT, IN, Pol</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Protease and reverse-transcriptase regions</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>37632071</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>37632071</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Not specified in the provided text</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>37674678</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>37674678</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ABI 3730XL</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2020-2021</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Whole Blood</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>37701387</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>DBS</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Dried blood spots</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NRTIs, INSTIs</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>37755428</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Tenofovir, lamivudine, dolutegravir</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>37817087</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>4559 and 3097</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>37823653</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>NFLG, gp120</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>37823653</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>plasma viral RNA</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>37872202</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>gp120</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>None reported</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>37878637</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>37878637</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>37878637</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, EFV</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, EFV, PI</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>37880705</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>37896785</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>37896785</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>d4T, 3TC, AZT, NVP</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>37914679</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Sanger sequencing, Illumina sequencing</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>MiSeq sequencing platform</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>37914679</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>37914679</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>TDF, FTC, EFV</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>37920909</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Whole Blood</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Viral RNA</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>820 or 46</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>37938856</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>37946329</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>37946329</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Were samples cloned prior to sequencing?</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>37957382</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Full genome, NFLG</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>37976080</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>37976080</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>37976185</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Sanger sequencing, NGS</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>37976185</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>TDF, FTC</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>TDF/TAF with FTC</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Were sequences from the paper made publicly available?</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>38005921</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>38020274</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>38020274</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>38033131</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>38033131</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>38058846</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>HIV from plasma</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>38072961</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Sanger sequencing, NGS</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>5</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Plasma, PBMC</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>38090027</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>BIC, FTC, TAF, EVG</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>38140553</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>K03455</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>38140553</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>38140553</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NRTIs, NNRTIs, PIs</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>38152686</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>38152686</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>37</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2008-2019</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2018-2019</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>High-throughput sequencing</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>NRTI, PI, NNRTI</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>38314093</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>38427738</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>38427738</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>38427738</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>38427738</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>38427738</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Not mentioned</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
           <t>38864613</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>RT, CA</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Gag, Pol</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>38864613</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
         <is>
           <t>What type of samples were sequenced?</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
         <is>
           <t>Plasma viral RNA</t>
         </is>
       </c>
-      <c r="E143" t="n">
+      <c r="E260" t="n">
         <v>0</v>
       </c>
     </row>

--- a/eval/learning-curve/results/learning_curve_ft200_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_ft200_incorrect.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4909,22 +4909,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>37632026</t>
+          <t>37632071</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>PR, RT, IN, Pol</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Protease and reverse-transcriptase regions</t>
+          <t>NRTI, INSTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NRTI, INSTI, NNRTI, PI</t>
+          <t>Not specified in the provided text</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -4959,22 +4959,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>37632071</t>
+          <t>37674678</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Not specified in the provided text</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>ABI 3730XL</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -5009,22 +5009,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>37674678</t>
+          <t>37701387</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ABI 3730XL</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -5039,17 +5039,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5139,17 +5139,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -5159,22 +5159,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>37701387</t>
+          <t>37755428</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>DBS</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dried blood spots</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5189,17 +5189,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>DBS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Dried blood spots</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTIs, INSTIs</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NRTIs, INSTIs</t>
+          <t>Tenofovir, lamivudine, dolutegravir</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -5284,22 +5284,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>37755428</t>
+          <t>37817087</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>4559 and 3097</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Tenofovir, lamivudine, dolutegravir</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -5309,22 +5309,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>37817087</t>
+          <t>37823653</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>4559 and 3097</t>
+          <t>NFLG, gp120</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>env</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>NFLG, gp120</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>env</t>
+          <t>plasma viral RNA</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -5359,22 +5359,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>37823653</t>
+          <t>37872202</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>gp120</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>plasma viral RNA</t>
+          <t>None reported</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -5384,22 +5384,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>37872202</t>
+          <t>37878637</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>gp120</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>None reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -5434,22 +5434,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37880705</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>PCR products were sequenced using the Applied Biosystems 3500 genetic analyzer</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5459,22 +5459,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>37878637</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>TDF, 3TC, EFV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>TDF, 3TC, EFV, PI</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -5484,22 +5484,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>37880705</t>
+          <t>37896785</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>d4T, 3TC, AZT, NVP</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5509,22 +5509,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37896860</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>RT, PI</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5534,22 +5534,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>37896785</t>
+          <t>37914679</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, Illumina sequencing</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>d4T, 3TC, AZT, NVP</t>
+          <t>MiSeq sequencing platform</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5564,17 +5564,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Sanger sequencing, Illumina sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>MiSeq sequencing platform</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>TDF, FTC, EFV</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -5609,22 +5609,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>37914679</t>
+          <t>37920909</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>TDF, FTC, EFV</t>
+          <t>Viral RNA</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5634,22 +5634,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>37920909</t>
+          <t>37938856</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>820 or 46</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Viral RNA</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5664,17 +5664,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>820 or 46</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -5684,12 +5684,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>37938856</t>
+          <t>37946329</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -5734,22 +5734,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>37946329</t>
+          <t>37957382</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>TDF, D4T, 3TC, ABC, AZT, FTC, NVP, EFV, RPV, ATV, FPV, LPV, SQV, RAL, ELV, DTG, BIC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Full genome, NFLG</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -5784,22 +5784,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>37957382</t>
+          <t>37976080</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Full genome, NFLG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Near-full length pro-viral HIV genomes; HIV-1 pol, env RNA</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -5834,22 +5834,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>37976080</t>
+          <t>37976185</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>abacavir, stavudine, emtricitabine, lamivudine, didanosine, zidovudine, tenofovir, atazanavir/r, lopinavir/r</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -5864,17 +5864,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>TDF, FTC</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>TDF/TAF with FTC</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -5884,22 +5884,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>37976185</t>
+          <t>38005921</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>TDF, FTC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>TDF/TAF with FTC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -5914,17 +5914,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -5939,17 +5939,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>The paper mentions the sequencing of protease and reverse transcriptase genes.</t>
+          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -5984,12 +5984,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>38005921</t>
+          <t>38020274</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>The paper mentions that amino acid sequences of HIV enzymes were used.</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -6034,12 +6034,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>38020274</t>
+          <t>38033131</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>TDF, 3TC, AZT, ABC, NVP, DLV, LPV, ATV, DRV</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -6084,22 +6084,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>38033131</t>
+          <t>38058846</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Zidovudine (AZT), Tenofovir (TDF), Stavudine (d4T), Emtricitabine (FTC) Nevirapine (NVP), Efavirenz (EFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -6114,17 +6114,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -6139,17 +6139,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>HIV from plasma</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -6159,22 +6159,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>38058846</t>
+          <t>38072961</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing, NGS</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>HIV from plasma</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6184,22 +6184,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>38072961</t>
+          <t>38090027</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Sanger sequencing, NGS</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -6214,17 +6214,15 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>5</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -6239,11 +6237,13 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C234" t="n">
-        <v>5</v>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -6262,12 +6262,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>BIC, FTC, TAF, EVG</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6432,22 +6432,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>38090027</t>
+          <t>38140553</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>BIC, FTC, TAF, EVG</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>K03455</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -6462,17 +6462,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>K03455</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -6487,17 +6487,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTIs, NNRTIs, PIs</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -6507,12 +6507,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>38140553</t>
+          <t>38152686</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NRTIs, NNRTIs, PIs</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -6537,17 +6537,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -6557,22 +6557,20 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>38152686</t>
+          <t>38314093</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>37</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -6587,15 +6585,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="C248" t="n">
-        <v>37</v>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2008-2019</t>
+        </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>2018-2019</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -6610,17 +6610,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2008-2019</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2018-2019</t>
+          <t>High-throughput sequencing</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -6635,17 +6635,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>High-throughput sequencing</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -6660,17 +6660,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, PI, NNRTI</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI</t>
+          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -6705,12 +6705,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>38314093</t>
+          <t>38427738</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>EFV, NVP, AZT, 3TC, tenofovir, abacavir</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6760,17 +6760,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -6785,17 +6785,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6830,22 +6830,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>38427738</t>
+          <t>38864613</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, CA</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>Gag, Pol</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -6860,45 +6860,20 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>RT, CA</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Gag, Pol</t>
+          <t>Plasma viral RNA</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>38864613</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>What type of samples were sequenced?</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Not reported</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Plasma viral RNA</t>
-        </is>
-      </c>
-      <c r="E260" t="n">
         <v>0</v>
       </c>
     </row>
